--- a/Database 1.xlsx
+++ b/Database 1.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4733EC11-5F02-409D-92BF-4625A861D9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63B1FF78-B252-4295-B3D4-5EC1F29912A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SampleData" sheetId="2" r:id="rId1"/>
-    <sheet name="Address Book" sheetId="1" r:id="rId2"/>
-    <sheet name="Snacks" sheetId="4" r:id="rId3"/>
-    <sheet name="Vending" sheetId="5" r:id="rId4"/>
-    <sheet name="Sales" sheetId="6" r:id="rId5"/>
+    <sheet name="Sample Data 2" sheetId="7" r:id="rId1"/>
+    <sheet name="SampleData" sheetId="2" r:id="rId2"/>
+    <sheet name="Address Book" sheetId="1" r:id="rId3"/>
+    <sheet name="Snacks" sheetId="4" r:id="rId4"/>
+    <sheet name="Vending" sheetId="5" r:id="rId5"/>
+    <sheet name="Sales" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,14 +37,104 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
+      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="110">
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\2fer.jpg</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\airheads.jpg</t>
+  </si>
+  <si>
+    <t>testing</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\extragum.jpg</t>
+  </si>
+  <si>
+    <t>tungsten</t>
+  </si>
+  <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>this is a test</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\almondjoy.png</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\juicyfruit.jpg</t>
+  </si>
+  <si>
+    <t>tests</t>
+  </si>
+  <si>
+    <t>test2</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  12   124</t>
+  </si>
+  <si>
+    <t>testasae</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests </t>
+  </si>
+  <si>
+    <t>charlie</t>
+  </si>
+  <si>
+    <t>hatch</t>
+  </si>
+  <si>
+    <t>this is a largeer scale test</t>
+  </si>
+  <si>
+    <t>large</t>
+  </si>
+  <si>
+    <t>this is a very large scale test and I do mean very as in very</t>
+  </si>
+  <si>
+    <t>test3</t>
+  </si>
+  <si>
+    <t>testt</t>
+  </si>
+  <si>
+    <t>4444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
   <si>
     <t>Index</t>
   </si>
@@ -109,9 +200,6 @@
   </si>
   <si>
     <t>Contains the phone number (with the normal phonenumber formating)</t>
-  </si>
-  <si>
-    <t>test</t>
   </si>
   <si>
     <t>email@email.email</t>
@@ -205,67 +293,10 @@
     <t>Not sure how, they got a soviute union website</t>
   </si>
   <si>
-    <t>testing</t>
-  </si>
-  <si>
-    <t>test2</t>
-  </si>
-  <si>
-    <t>tests</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  12   124</t>
-  </si>
-  <si>
-    <t>testasae</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>hi</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests </t>
-  </si>
-  <si>
-    <t>charlie</t>
-  </si>
-  <si>
-    <t>hatch</t>
-  </si>
-  <si>
-    <t>this is a largeer scale test</t>
-  </si>
-  <si>
-    <t>large</t>
-  </si>
-  <si>
-    <t>this is a very large scale test and I do mean very as in very</t>
-  </si>
-  <si>
-    <t>test3</t>
-  </si>
-  <si>
-    <t>testt</t>
-  </si>
-  <si>
-    <t>4444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
-  </si>
-  <si>
-    <t>info</t>
+    <t>size</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
   <si>
     <t>numeric</t>
@@ -280,10 +311,7 @@
     <t>bit</t>
   </si>
   <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>?</t>
+    <t>SnackID</t>
   </si>
   <si>
     <t>Name</t>
@@ -298,6 +326,12 @@
     <t>Image Path</t>
   </si>
   <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Valid</t>
+  </si>
+  <si>
     <t>Field</t>
   </si>
   <si>
@@ -310,47 +344,44 @@
     <t>description</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>uuid for said entry</t>
+  </si>
+  <si>
+    <t>char(30)</t>
+  </si>
+  <si>
+    <t>name of the snack</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>smallmoney</t>
+  </si>
+  <si>
+    <t>price of snack</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>name of the snack</t>
-  </si>
-  <si>
-    <t>price of snack</t>
-  </si>
-  <si>
-    <t>int</t>
+    <t>tinyint</t>
   </si>
   <si>
     <t>quantity of snack</t>
   </si>
   <si>
     <t>path of image</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>char(30)</t>
-  </si>
-  <si>
-    <t>smallmoney</t>
-  </si>
-  <si>
-    <t>tinyint</t>
-  </si>
-  <si>
-    <t>SnackID</t>
-  </si>
-  <si>
-    <t>uuid for said entry</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,7 +433,13 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -423,7 +460,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{962C7140-9458-4E7F-884A-6E9A4E8487F2}" name="Table1" displayName="Table1" ref="A1:G11" totalsRowShown="0">
   <autoFilter ref="A1:G11" xr:uid="{962C7140-9458-4E7F-884A-6E9A4E8487F2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{60AA6AD5-C93C-4B92-85FF-D77DD40E87A5}" name="Index" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{60AA6AD5-C93C-4B92-85FF-D77DD40E87A5}" name="Index" dataDxfId="2">
       <calculatedColumnFormula>IF(ISNUMBER(A1),A1+1,0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{54099B7A-9B8C-482B-8083-4CA8C5275D84}" name="First Name"/>
@@ -438,23 +475,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:E5" totalsRowShown="0">
-  <autoFilter ref="A1:E5" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
-  <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:G5" totalsRowShown="0">
+  <autoFilter ref="A1:G5" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
+  <tableColumns count="7">
+    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID" dataDxfId="1">
+      <calculatedColumnFormula>IF(ISNUMBER(A1),A1+1,1)</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="1" xr3:uid="{E195EB5F-6D4B-42C3-8801-919637F30006}" name="Name"/>
     <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price"/>
     <tableColumn id="3" xr3:uid="{191A4393-993C-4AB5-9310-5337B03C07D3}" name="Quantity On Hand"/>
     <tableColumn id="4" xr3:uid="{01AF8722-0E57-4D45-8F72-AD068B958406}" name="Image Path"/>
+    <tableColumn id="6" xr3:uid="{85B6F931-9CA9-4FF4-9FB1-406FC9E56BA6}" name="Column1"/>
+    <tableColumn id="7" xr3:uid="{AEC76C43-8C35-4A51-B34A-C477D5C7F079}" name="Valid" dataDxfId="0">
+      <calculatedColumnFormula>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -492,7 +535,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -598,7 +641,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -740,16 +783,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28EEB29-88E9-4F91-A919-2DF8C70E2648}">
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ECEA5BB-8E4E-42E6-AD28-A777D9306799}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
@@ -759,422 +802,191 @@
     <col min="7" max="7" width="3.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.05</v>
       </c>
       <c r="C1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" t="s">
-        <v>54</v>
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0.7</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.05</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4">
-        <v>11</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C5">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5">
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C6">
+        <v>97</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6">
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>0.08</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8">
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
+      <c r="B9">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>11</v>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>0.05</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>0.05</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
         <v>3</v>
       </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-      <c r="G10">
+      <c r="E11">
         <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12">
-        <v>1234567891</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>1</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>1234567890</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1183,9 +995,445 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28EEB29-88E9-4F91-A919-2DF8C70E2648}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>11</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>11</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12">
+        <v>1234567891</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1234567890</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -1200,342 +1448,342 @@
     <col min="13" max="13" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="30">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="30">
       <c r="A2">
         <f t="shared" ref="A2:A11" si="0">IF(ISNUMBER(A1),A1+1,0)</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>2345678901</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="K2" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="45">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="D3">
         <v>2811111111</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>2209371286</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="30">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>9876111121</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="O5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="D6">
         <v>1291821021</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="D7">
         <v>1234543201</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>1234562311</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="D9">
         <v>1234567812</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="D11">
         <v>2312121212</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -1544,68 +1792,68 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
       <c r="P23" s="1"/>
       <c r="W23" t="s">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="X23" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="Y23">
         <v>1</v>
       </c>
       <c r="Z23" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="AC23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29">
       <c r="W24" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="X24" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="Y24">
         <v>2</v>
       </c>
       <c r="Z24" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="b">
         <v>1</v>
       </c>
       <c r="AB24" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="AC24">
         <v>3</v>
@@ -1634,117 +1882,156 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7BC218-E894-43DE-BEC3-7A8A07868B41}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I2" t="s">
-        <v>91</v>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2">
+        <f t="shared" ref="A2:A5" si="0">IF(ISNUMBER(A1),A1+1,1)</f>
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I3" t="s">
-        <v>35</v>
+      <c r="L2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G3" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I4" t="s">
-        <v>94</v>
+        <v>64</v>
+      </c>
+      <c r="L3" t="s">
+        <v>101</v>
+      </c>
+      <c r="M3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G4" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H5" t="s">
-        <v>88</v>
-      </c>
-      <c r="I5" t="s">
-        <v>91</v>
+        <v>103</v>
+      </c>
+      <c r="L4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="K5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" t="s">
+        <v>107</v>
+      </c>
+      <c r="M5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="J6" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" t="s">
-        <v>76</v>
-      </c>
       <c r="K6" t="s">
-        <v>93</v>
+        <v>64</v>
+      </c>
+      <c r="L6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M6" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1755,19 +2042,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E27DB38-9B86-476F-ADB3-257C50139E20}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1932462C-482C-40F7-8C16-E10683B0C6A3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Database 1.xlsx
+++ b/Database 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63B1FF78-B252-4295-B3D4-5EC1F29912A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEA1EE3A-794B-47C0-862C-F8126F7AECA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample Data 2" sheetId="7" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="115">
   <si>
     <t>Test</t>
   </si>
@@ -344,12 +344,18 @@
     <t>description</t>
   </si>
   <si>
+    <t>2fer.jpg</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>uuid for said entry</t>
   </si>
   <si>
+    <t>airheads.jpg</t>
+  </si>
+  <si>
     <t>char(30)</t>
   </si>
   <si>
@@ -365,6 +371,9 @@
     <t>price of snack</t>
   </si>
   <si>
+    <t>extragum.jpg</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
@@ -375,13 +384,22 @@
   </si>
   <si>
     <t>path of image</t>
+  </si>
+  <si>
+    <t>almondjoy.png</t>
+  </si>
+  <si>
+    <t>juicyfruit.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,6 +414,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -419,7 +443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -428,14 +452,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -460,7 +490,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{962C7140-9458-4E7F-884A-6E9A4E8487F2}" name="Table1" displayName="Table1" ref="A1:G11" totalsRowShown="0">
   <autoFilter ref="A1:G11" xr:uid="{962C7140-9458-4E7F-884A-6E9A4E8487F2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{60AA6AD5-C93C-4B92-85FF-D77DD40E87A5}" name="Index" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{60AA6AD5-C93C-4B92-85FF-D77DD40E87A5}" name="Index" dataDxfId="3">
       <calculatedColumnFormula>IF(ISNUMBER(A1),A1+1,0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{54099B7A-9B8C-482B-8083-4CA8C5275D84}" name="First Name"/>
@@ -475,14 +505,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:G5" totalsRowShown="0">
-  <autoFilter ref="A1:G5" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:G12" totalsRowShown="0">
+  <autoFilter ref="A1:G12" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
   <tableColumns count="7">
-    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID" dataDxfId="2">
       <calculatedColumnFormula>IF(ISNUMBER(A1),A1+1,1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="1" xr3:uid="{E195EB5F-6D4B-42C3-8801-919637F30006}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price"/>
+    <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{191A4393-993C-4AB5-9310-5337B03C07D3}" name="Quantity On Hand"/>
     <tableColumn id="4" xr3:uid="{01AF8722-0E57-4D45-8F72-AD068B958406}" name="Image Path"/>
     <tableColumn id="6" xr3:uid="{85B6F931-9CA9-4FF4-9FB1-406FC9E56BA6}" name="Column1"/>
@@ -1884,11 +1914,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7BC218-E894-43DE-BEC3-7A8A07868B41}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="4" customWidth="1"/>
     <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -1904,7 +1934,7 @@
       <c r="B1" t="s">
         <v>89</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D1" t="s">
@@ -1937,6 +1967,18 @@
         <f t="shared" ref="A2:A5" si="0">IF(ISNUMBER(A1),A1+1,1)</f>
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>99</v>
+      </c>
       <c r="G2" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
         <v>1</v>
@@ -1945,13 +1987,13 @@
         <v>88</v>
       </c>
       <c r="K2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1959,9 +2001,21 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="G3" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="s">
         <v>89</v>
@@ -1970,10 +2024,10 @@
         <v>64</v>
       </c>
       <c r="L3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1981,6 +2035,18 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="D4">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>99</v>
+      </c>
       <c r="G4" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
         <v>1</v>
@@ -1989,13 +2055,13 @@
         <v>90</v>
       </c>
       <c r="K4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2003,24 +2069,56 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>108</v>
+      </c>
       <c r="G5" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:13">
+      <c r="A6" s="5">
+        <f>IF(ISNUMBER(A5),A5+1,1)</f>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D6">
+        <v>33</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <v>0</v>
+      </c>
       <c r="J6" t="s">
         <v>92</v>
       </c>
@@ -2031,7 +2129,142 @@
         <v>86</v>
       </c>
       <c r="M6" t="s">
-        <v>109</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="5">
+        <f>IF(ISNUMBER(A6),A6+1,1)</f>
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D7">
+        <v>97</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="5">
+        <f>IF(ISNUMBER(A7),A7+1,1)</f>
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="5">
+        <f>IF(ISNUMBER(A8),A8+1,1)</f>
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G9" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5">
+        <f>IF(ISNUMBER(A9),A9+1,1)</f>
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G10" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5">
+        <f>IF(ISNUMBER(A10),A10+1,1)</f>
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="5">
+        <f>IF(ISNUMBER(A11),A11+1,1)</f>
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Database 1.xlsx
+++ b/Database 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEA1EE3A-794B-47C0-862C-F8126F7AECA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A261A577-2A4D-4EF5-B1E6-C341028E30A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -517,7 +517,7 @@
     <tableColumn id="4" xr3:uid="{01AF8722-0E57-4D45-8F72-AD068B958406}" name="Image Path"/>
     <tableColumn id="6" xr3:uid="{85B6F931-9CA9-4FF4-9FB1-406FC9E56BA6}" name="Column1"/>
     <tableColumn id="7" xr3:uid="{AEC76C43-8C35-4A51-B34A-C477D5C7F079}" name="Valid" dataDxfId="0">
-      <calculatedColumnFormula>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1980,7 +1980,7 @@
         <v>99</v>
       </c>
       <c r="G2" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
         <v>1</v>
       </c>
       <c r="J2" t="s">
@@ -2013,9 +2013,9 @@
       <c r="E3" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="G3" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
-        <v>0</v>
+      <c r="G3" t="str">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>FALSE 12</v>
       </c>
       <c r="J3" t="s">
         <v>89</v>
@@ -2048,7 +2048,7 @@
         <v>99</v>
       </c>
       <c r="G4" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
         <v>1</v>
       </c>
       <c r="J4" t="s">
@@ -2081,9 +2081,9 @@
       <c r="E5" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
-        <v>0</v>
+      <c r="G5" t="str">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>FALSE 12</v>
       </c>
       <c r="J5" t="s">
         <v>109</v>
@@ -2115,9 +2115,9 @@
       <c r="E6" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
-        <v>0</v>
+      <c r="G6" s="5" t="str">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>FALSE 12</v>
       </c>
       <c r="J6" t="s">
         <v>92</v>
@@ -2149,9 +2149,9 @@
       <c r="E7" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="G7" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
-        <v>0</v>
+      <c r="G7" s="5" t="str">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>FALSE 12</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -2174,9 +2174,9 @@
       <c r="E8" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="G8" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
-        <v>0</v>
+      <c r="G8" s="5" t="str">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>FALSE 13</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2196,9 +2196,9 @@
       <c r="E9" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="G9" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
-        <v>0</v>
+      <c r="G9" s="5" t="str">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>FALSE 13</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2218,9 +2218,9 @@
       <c r="E10" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="G10" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
-        <v>0</v>
+      <c r="G10" s="5" t="str">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>FALSE 14</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2241,7 +2241,7 @@
         <v>99</v>
       </c>
       <c r="G11" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
         <v>1</v>
       </c>
     </row>
@@ -2262,9 +2262,9 @@
       <c r="E12" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),FALSE())</f>
-        <v>0</v>
+      <c r="G12" s="5" t="str">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>FALSE 12</v>
       </c>
     </row>
   </sheetData>

--- a/Database 1.xlsx
+++ b/Database 1.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A261A577-2A4D-4EF5-B1E6-C341028E30A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7017824F-7220-4F73-A929-5C805913F6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sample Data 2" sheetId="7" r:id="rId1"/>
-    <sheet name="SampleData" sheetId="2" r:id="rId2"/>
-    <sheet name="Address Book" sheetId="1" r:id="rId3"/>
-    <sheet name="Snacks" sheetId="4" r:id="rId4"/>
-    <sheet name="Vending" sheetId="5" r:id="rId5"/>
-    <sheet name="Sales" sheetId="6" r:id="rId6"/>
+    <sheet name="Dev Notes" sheetId="8" r:id="rId1"/>
+    <sheet name="Sample Data 2" sheetId="7" r:id="rId2"/>
+    <sheet name="SampleData" sheetId="2" r:id="rId3"/>
+    <sheet name="Address Book" sheetId="1" r:id="rId4"/>
+    <sheet name="Snacks" sheetId="4" r:id="rId5"/>
+    <sheet name="Vending" sheetId="5" r:id="rId6"/>
+    <sheet name="Sales" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -44,7 +45,121 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="148">
+  <si>
+    <t>📋 Snack Shack - Dev Notes</t>
+  </si>
+  <si>
+    <t>Track implemented concepts, schema decisions, and design rationale</t>
+  </si>
+  <si>
+    <t>✅ Implemented Concepts</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>Date Implemented</t>
+  </si>
+  <si>
+    <t>Sheet/Location</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>CSV to Spreadsheet parsing</t>
+  </si>
+  <si>
+    <t>Sample Data 2</t>
+  </si>
+  <si>
+    <t>Split comma-separated values into columns A-E</t>
+  </si>
+  <si>
+    <t>🗄️ Schema Decisions</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Rationale</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Snacks</t>
+  </si>
+  <si>
+    <t>SnackID</t>
+  </si>
+  <si>
+    <t>1-based indexing</t>
+  </si>
+  <si>
+    <t>SQL identity convention, human-readable</t>
+  </si>
+  <si>
+    <t>Image Path</t>
+  </si>
+  <si>
+    <t>Store filename only (no ext?)</t>
+  </si>
+  <si>
+    <t>TBD: char(10) constraint, reconstruct path in app</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>smallmoney</t>
+  </si>
+  <si>
+    <t>Sufficient precision for snack prices</t>
+  </si>
+  <si>
+    <t>❓ Open Questions / To-Do</t>
+  </si>
+  <si>
+    <t>Question/Task</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Resolution</t>
+  </si>
+  <si>
+    <t>Image path strategy: extension handling</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Options: strip ext + standardize .jpg, or dynamic detection</t>
+  </si>
+  <si>
+    <t>Valid column purpose</t>
+  </si>
+  <si>
+    <t>Planned</t>
+  </si>
+  <si>
+    <t>Path length validation testing</t>
+  </si>
+  <si>
+    <t>Vending/Sales table schema</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
   <si>
     <t>Test</t>
   </si>
@@ -152,9 +267,6 @@
   </si>
   <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Validated</t>
@@ -311,30 +423,18 @@
     <t>bit</t>
   </si>
   <si>
-    <t>SnackID</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Price</t>
-  </si>
-  <si>
     <t>Quantity On Hand</t>
   </si>
   <si>
-    <t>Image Path</t>
-  </si>
-  <si>
     <t>Column1</t>
   </si>
   <si>
     <t>Valid</t>
   </si>
   <si>
-    <t>Field</t>
-  </si>
-  <si>
     <t>C# Data Type</t>
   </si>
   <si>
@@ -356,7 +456,7 @@
     <t>airheads.jpg</t>
   </si>
   <si>
-    <t>char(30)</t>
+    <t>varchar(30)</t>
   </si>
   <si>
     <t>name of the snack</t>
@@ -365,9 +465,6 @@
     <t>float</t>
   </si>
   <si>
-    <t>smallmoney</t>
-  </si>
-  <si>
     <t>price of snack</t>
   </si>
   <si>
@@ -381,6 +478,9 @@
   </si>
   <si>
     <t>quantity of snack</t>
+  </si>
+  <si>
+    <t>varchar(15)</t>
   </si>
   <si>
     <t>path of image</t>
@@ -399,7 +499,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,13 +521,76 @@
       <name val="Aptos Narrow"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -443,7 +606,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -455,6 +618,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -517,7 +688,7 @@
     <tableColumn id="4" xr3:uid="{01AF8722-0E57-4D45-8F72-AD068B958406}" name="Image Path"/>
     <tableColumn id="6" xr3:uid="{85B6F931-9CA9-4FF4-9FB1-406FC9E56BA6}" name="Column1"/>
     <tableColumn id="7" xr3:uid="{AEC76C43-8C35-4A51-B34A-C477D5C7F079}" name="Valid" dataDxfId="0">
-      <calculatedColumnFormula>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -820,6 +991,186 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C3DB4FA-A95C-4424-BD58-265C1159E376}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="41.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" customWidth="1"/>
+    <col min="4" max="4" width="53.28515625" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75">
+      <c r="A4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="12">
+        <v>46153</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75">
+      <c r="A9" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="12">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="12">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75">
+      <c r="A16" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ECEA5BB-8E4E-42E6-AD28-A777D9306799}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -834,7 +1185,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B1">
         <v>0.05</v>
@@ -843,7 +1194,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E1">
         <v>0</v>
@@ -851,7 +1202,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>7.0000000000000007E-2</v>
@@ -860,7 +1211,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -868,7 +1219,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>0.7</v>
@@ -877,7 +1228,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -885,7 +1236,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>0.05</v>
@@ -894,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -902,7 +1253,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>7.0000000000000007E-2</v>
@@ -911,7 +1262,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -919,7 +1270,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="B6">
         <v>7.0000000000000007E-2</v>
@@ -928,7 +1279,7 @@
         <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -936,7 +1287,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B7">
         <v>0.08</v>
@@ -945,7 +1296,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -953,7 +1304,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>7.0000000000000007E-2</v>
@@ -962,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -970,7 +1321,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B9">
         <v>7.0000000000000007E-2</v>
@@ -979,7 +1330,7 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -987,7 +1338,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>0.05</v>
@@ -996,7 +1347,7 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1004,7 +1355,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>0.05</v>
@@ -1013,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1024,7 +1375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28EEB29-88E9-4F91-A919-2DF8C70E2648}">
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1039,22 +1390,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C1">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E1" t="b">
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="G1">
         <v>1</v>
@@ -1062,22 +1413,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1085,22 +1436,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1108,10 +1459,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="D4">
         <v>11</v>
@@ -1128,22 +1479,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1151,22 +1502,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1174,13 +1525,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1189,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -1197,13 +1548,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1212,7 +1563,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -1220,10 +1571,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1235,7 +1586,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="G9">
         <v>9</v>
@@ -1266,10 +1617,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1281,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="G11">
         <v>11</v>
@@ -1289,22 +1640,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C12">
         <v>1234567891</v>
       </c>
       <c r="D12" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>12</v>
@@ -1312,42 +1663,42 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="G14">
         <v>14</v>
@@ -1355,7 +1706,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -1366,7 +1717,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -1377,7 +1728,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -1388,22 +1739,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="G18">
         <v>18</v>
@@ -1426,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="G19">
         <v>19</v>
@@ -1434,22 +1785,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="G20">
         <v>20</v>
@@ -1460,7 +1811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC24"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1480,37 +1831,37 @@
   <sheetData>
     <row r="1" spans="1:15" ht="30">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="E1" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="J1" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="K1" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="30">
@@ -1519,32 +1870,32 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="D2">
         <v>2345678901</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="45">
@@ -1553,32 +1904,32 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="D3">
         <v>2811111111</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1587,32 +1938,32 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>2209371286</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="30">
@@ -1621,35 +1972,35 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D5">
         <v>9876111121</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="K5" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="O5" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1658,29 +2009,29 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="D6">
         <v>1291821021</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="K6" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1689,16 +2040,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="D7">
         <v>1234543201</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1710,22 +2061,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D8">
         <v>1234562311</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1734,22 +2085,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="D9">
         <v>1234567812</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1758,22 +2109,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1782,38 +2133,38 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="D11">
         <v>2312121212</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:29">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:29">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -1824,43 +2175,43 @@
     </row>
     <row r="19" spans="1:29">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="F19" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:29">
       <c r="P23" s="1"/>
       <c r="W23" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="X23" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="Y23">
         <v>1</v>
       </c>
       <c r="Z23" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AC23">
         <v>2</v>
@@ -1868,22 +2219,22 @@
     </row>
     <row r="24" spans="1:29">
       <c r="W24" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="X24" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="Y24">
         <v>2</v>
       </c>
       <c r="Z24" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AA24" t="b">
         <v>1</v>
       </c>
       <c r="AB24" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AC24">
         <v>3</v>
@@ -1912,7 +2263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7BC218-E894-43DE-BEC3-7A8A07868B41}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1929,37 +2280,37 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="E1" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="G1" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="J1" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="K1" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="L1" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="M1" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1968,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C2" s="4">
         <v>0.05</v>
@@ -1977,23 +2328,23 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="G2" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="K2" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L2" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="M2" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2002,7 +2353,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C3" s="4">
         <v>7.0000000000000007E-2</v>
@@ -2011,23 +2362,23 @@
         <v>1</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G3" t="str">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>FALSE 12</v>
+        <v>135</v>
+      </c>
+      <c r="G3" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="K3" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="L3" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="M3" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2036,7 +2387,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C4" s="4">
         <v>0.7</v>
@@ -2045,23 +2396,23 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="G4" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="K4" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="L4" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="M4" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2070,7 +2421,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="C5" s="4">
         <v>0.05</v>
@@ -2079,23 +2430,23 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" t="str">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>FALSE 12</v>
+        <v>140</v>
+      </c>
+      <c r="G5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="K5" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L5" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="M5" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2104,7 +2455,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C6" s="4">
         <v>7.0000000000000007E-2</v>
@@ -2113,23 +2464,23 @@
         <v>33</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" s="5" t="str">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>FALSE 12</v>
+        <v>135</v>
+      </c>
+      <c r="G6" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="L6" t="s">
-        <v>86</v>
+        <v>144</v>
       </c>
       <c r="M6" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2138,7 +2489,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C7" s="4">
         <v>7.0000000000000007E-2</v>
@@ -2147,14 +2498,14 @@
         <v>97</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="5" t="str">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>FALSE 12</v>
+        <v>135</v>
+      </c>
+      <c r="G7" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2163,7 +2514,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4">
         <v>0.08</v>
@@ -2172,11 +2523,11 @@
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="G8" s="5" t="str">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>FALSE 13</v>
+        <v>146</v>
+      </c>
+      <c r="G8" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2185,7 +2536,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C9" s="4">
         <v>7.0000000000000007E-2</v>
@@ -2194,11 +2545,11 @@
         <v>1</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="G9" s="5" t="str">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>FALSE 13</v>
+        <v>146</v>
+      </c>
+      <c r="G9" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2207,7 +2558,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="C10" s="4">
         <v>7.0000000000000007E-2</v>
@@ -2216,11 +2567,11 @@
         <v>2</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G10" s="5" t="str">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>FALSE 14</v>
+        <v>147</v>
+      </c>
+      <c r="G10" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2229,7 +2580,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C11" s="4">
         <v>0.05</v>
@@ -2238,10 +2589,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="G11" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
         <v>1</v>
       </c>
     </row>
@@ -2251,7 +2602,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C12" s="4">
         <v>0.05</v>
@@ -2260,11 +2611,11 @@
         <v>0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" s="5" t="str">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE()," ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>FALSE 12</v>
+        <v>135</v>
+      </c>
+      <c r="G12" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2275,7 +2626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E27DB38-9B86-476F-ADB3-257C50139E20}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2284,7 +2635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1932462C-482C-40F7-8C16-E10683B0C6A3}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/Database 1.xlsx
+++ b/Database 1.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7017824F-7220-4F73-A929-5C805913F6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5223914A-20AF-453B-85CD-D56106D83657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dev Notes" sheetId="8" r:id="rId1"/>
-    <sheet name="Sample Data 2" sheetId="7" r:id="rId2"/>
-    <sheet name="SampleData" sheetId="2" r:id="rId3"/>
-    <sheet name="Address Book" sheetId="1" r:id="rId4"/>
-    <sheet name="Snacks" sheetId="4" r:id="rId5"/>
-    <sheet name="Vending" sheetId="5" r:id="rId6"/>
-    <sheet name="Sales" sheetId="6" r:id="rId7"/>
+    <sheet name="Sample Data 2" sheetId="7" r:id="rId1"/>
+    <sheet name="SampleData" sheetId="2" r:id="rId2"/>
+    <sheet name="Address Book" sheetId="1" r:id="rId3"/>
+    <sheet name="Snacks" sheetId="4" r:id="rId4"/>
+    <sheet name="Vending" sheetId="5" r:id="rId5"/>
+    <sheet name="Sales" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,228 +44,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="148">
-  <si>
-    <t>📋 Snack Shack - Dev Notes</t>
-  </si>
-  <si>
-    <t>Track implemented concepts, schema decisions, and design rationale</t>
-  </si>
-  <si>
-    <t>✅ Implemented Concepts</t>
-  </si>
-  <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>Date Implemented</t>
-  </si>
-  <si>
-    <t>Sheet/Location</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="116">
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\2fer.jpg</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\airheads.jpg</t>
+  </si>
+  <si>
+    <t>testing</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\extragum.jpg</t>
+  </si>
+  <si>
+    <t>tungsten</t>
+  </si>
+  <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>this is a test</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\almondjoy.png</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\juicyfruit.jpg</t>
+  </si>
+  <si>
+    <t>tests</t>
+  </si>
+  <si>
+    <t>test2</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  12   124</t>
+  </si>
+  <si>
+    <t>testasae</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests </t>
+  </si>
+  <si>
+    <t>charlie</t>
+  </si>
+  <si>
+    <t>hatch</t>
+  </si>
+  <si>
+    <t>this is a largeer scale test</t>
+  </si>
+  <si>
+    <t>large</t>
+  </si>
+  <si>
+    <t>this is a very large scale test and I do mean very as in very</t>
+  </si>
+  <si>
+    <t>test3</t>
+  </si>
+  <si>
+    <t>testt</t>
+  </si>
+  <si>
+    <t>4444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Type</t>
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>CSV to Spreadsheet parsing</t>
-  </si>
-  <si>
-    <t>Sample Data 2</t>
-  </si>
-  <si>
-    <t>Split comma-separated values into columns A-E</t>
-  </si>
-  <si>
-    <t>🗄️ Schema Decisions</t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>Rationale</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Snacks</t>
-  </si>
-  <si>
-    <t>SnackID</t>
-  </si>
-  <si>
-    <t>1-based indexing</t>
-  </si>
-  <si>
-    <t>SQL identity convention, human-readable</t>
-  </si>
-  <si>
-    <t>Image Path</t>
-  </si>
-  <si>
-    <t>Store filename only (no ext?)</t>
-  </si>
-  <si>
-    <t>TBD: char(10) constraint, reconstruct path in app</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>smallmoney</t>
-  </si>
-  <si>
-    <t>Sufficient precision for snack prices</t>
-  </si>
-  <si>
-    <t>❓ Open Questions / To-Do</t>
-  </si>
-  <si>
-    <t>Question/Task</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Resolution</t>
-  </si>
-  <si>
-    <t>Image path strategy: extension handling</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>Options: strip ext + standardize .jpg, or dynamic detection</t>
-  </si>
-  <si>
-    <t>Valid column purpose</t>
-  </si>
-  <si>
-    <t>Planned</t>
-  </si>
-  <si>
-    <t>Path length validation testing</t>
-  </si>
-  <si>
-    <t>Vending/Sales table schema</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\2fer.jpg</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\airheads.jpg</t>
-  </si>
-  <si>
-    <t>testing</t>
-  </si>
-  <si>
-    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\extragum.jpg</t>
-  </si>
-  <si>
-    <t>tungsten</t>
-  </si>
-  <si>
-    <t>hi</t>
-  </si>
-  <si>
-    <t>this is a test</t>
-  </si>
-  <si>
-    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\almondjoy.png</t>
-  </si>
-  <si>
-    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\juicyfruit.jpg</t>
-  </si>
-  <si>
-    <t>tests</t>
-  </si>
-  <si>
-    <t>test2</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  12   124</t>
-  </si>
-  <si>
-    <t>testasae</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests </t>
-  </si>
-  <si>
-    <t>charlie</t>
-  </si>
-  <si>
-    <t>hatch</t>
-  </si>
-  <si>
-    <t>this is a largeer scale test</t>
-  </si>
-  <si>
-    <t>large</t>
-  </si>
-  <si>
-    <t>this is a very large scale test and I do mean very as in very</t>
-  </si>
-  <si>
-    <t>test3</t>
-  </si>
-  <si>
-    <t>testt</t>
-  </si>
-  <si>
-    <t>4444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
-  </si>
-  <si>
-    <t>info</t>
-  </si>
-  <si>
-    <t>Index</t>
-  </si>
-  <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Type</t>
   </si>
   <si>
     <t>Validated</t>
@@ -423,18 +311,30 @@
     <t>bit</t>
   </si>
   <si>
+    <t>SnackID</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
+    <t>Price</t>
+  </si>
+  <si>
     <t>Quantity On Hand</t>
   </si>
   <si>
+    <t>Image Path</t>
+  </si>
+  <si>
     <t>Column1</t>
   </si>
   <si>
     <t>Valid</t>
   </si>
   <si>
+    <t>Field</t>
+  </si>
+  <si>
     <t>C# Data Type</t>
   </si>
   <si>
@@ -463,6 +363,9 @@
   </si>
   <si>
     <t>float</t>
+  </si>
+  <si>
+    <t>smallmoney</t>
   </si>
   <si>
     <t>price of snack</t>
@@ -499,7 +402,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -521,76 +424,13 @@
       <name val="Aptos Narrow"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF808080"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -606,7 +446,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -618,14 +458,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -991,186 +823,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C3DB4FA-A95C-4424-BD58-265C1159E376}">
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="41.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" customWidth="1"/>
-    <col min="4" max="4" width="53.28515625" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75">
-      <c r="A4" s="9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="12">
-        <v>46153</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75">
-      <c r="A9" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="12">
-        <v>46153</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="12">
-        <v>46153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="12">
-        <v>46153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.75">
-      <c r="A16" s="14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="11"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ECEA5BB-8E4E-42E6-AD28-A777D9306799}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1185,7 +837,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B1">
         <v>0.05</v>
@@ -1194,7 +846,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E1">
         <v>0</v>
@@ -1202,7 +854,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>7.0000000000000007E-2</v>
@@ -1211,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1219,7 +871,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>0.7</v>
@@ -1228,7 +880,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1236,7 +888,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>0.05</v>
@@ -1245,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1253,7 +905,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>7.0000000000000007E-2</v>
@@ -1262,7 +914,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1270,7 +922,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>7.0000000000000007E-2</v>
@@ -1279,7 +931,7 @@
         <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1287,7 +939,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0.08</v>
@@ -1296,7 +948,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1304,7 +956,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B8">
         <v>7.0000000000000007E-2</v>
@@ -1313,7 +965,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1321,7 +973,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>7.0000000000000007E-2</v>
@@ -1330,7 +982,7 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1338,7 +990,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B10">
         <v>0.05</v>
@@ -1347,7 +999,7 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1355,7 +1007,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B11">
         <v>0.05</v>
@@ -1364,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1375,7 +1027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28EEB29-88E9-4F91-A919-2DF8C70E2648}">
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1390,22 +1042,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C1">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E1" t="b">
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G1">
         <v>1</v>
@@ -1413,22 +1065,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1436,22 +1088,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1459,10 +1111,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>11</v>
@@ -1479,22 +1131,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1502,22 +1154,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1525,13 +1177,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1540,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -1548,13 +1200,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1563,7 +1215,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -1571,10 +1223,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1586,7 +1238,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>9</v>
@@ -1617,10 +1269,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1632,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>11</v>
@@ -1640,22 +1292,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>1234567891</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G12">
         <v>12</v>
@@ -1663,42 +1315,42 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="G14">
         <v>14</v>
@@ -1706,7 +1358,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -1717,7 +1369,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -1728,7 +1380,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -1739,22 +1391,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C18">
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="G18">
         <v>18</v>
@@ -1777,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="G19">
         <v>19</v>
@@ -1785,22 +1437,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G20">
         <v>20</v>
@@ -1811,7 +1463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC24"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1831,37 +1483,37 @@
   <sheetData>
     <row r="1" spans="1:15" ht="30">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="J1" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="K1" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="30">
@@ -1870,32 +1522,32 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>2345678901</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="K2" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="45">
@@ -1904,32 +1556,32 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D3">
         <v>2811111111</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1938,32 +1590,32 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>2209371286</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="30">
@@ -1972,35 +1624,35 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>9876111121</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="O5" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -2009,29 +1661,29 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D6">
         <v>1291821021</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -2040,16 +1692,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="D7">
         <v>1234543201</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -2061,22 +1713,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>1234562311</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -2085,22 +1737,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="D9">
         <v>1234567812</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -2109,22 +1761,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -2133,38 +1785,38 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D11">
         <v>2312121212</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:29">
       <c r="A17" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:29">
       <c r="A18" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -2175,43 +1827,43 @@
     </row>
     <row r="19" spans="1:29">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="F19" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:29">
       <c r="P23" s="1"/>
       <c r="W23" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="X23" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="Y23">
         <v>1</v>
       </c>
       <c r="Z23" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="AC23">
         <v>2</v>
@@ -2219,22 +1871,22 @@
     </row>
     <row r="24" spans="1:29">
       <c r="W24" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="X24" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="Y24">
         <v>2</v>
       </c>
       <c r="Z24" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="b">
         <v>1</v>
       </c>
       <c r="AB24" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="AC24">
         <v>3</v>
@@ -2263,7 +1915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7BC218-E894-43DE-BEC3-7A8A07868B41}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2280,37 +1932,37 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="B1" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="D1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="F1" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="G1" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="J1" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="K1" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="L1" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="M1" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2319,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C2" s="4">
         <v>0.05</v>
@@ -2328,23 +1980,23 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="G2" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="K2" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="L2" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="M2" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2353,7 +2005,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4">
         <v>7.0000000000000007E-2</v>
@@ -2362,23 +2014,23 @@
         <v>1</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="G3" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="L3" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="M3" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2387,7 +2039,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C4" s="4">
         <v>0.7</v>
@@ -2396,23 +2048,23 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="G4" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="M4" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2421,7 +2073,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="C5" s="4">
         <v>0.05</v>
@@ -2430,23 +2082,23 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="G5" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="K5" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="M5" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2455,7 +2107,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C6" s="4">
         <v>7.0000000000000007E-2</v>
@@ -2464,23 +2116,23 @@
         <v>33</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="G6" s="5" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="K6" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="L6" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2489,7 +2141,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4">
         <v>7.0000000000000007E-2</v>
@@ -2498,7 +2150,7 @@
         <v>97</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="G7" s="5" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
@@ -2514,7 +2166,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4">
         <v>0.08</v>
@@ -2523,7 +2175,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="G8" s="5" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
@@ -2536,7 +2188,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C9" s="4">
         <v>7.0000000000000007E-2</v>
@@ -2545,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="G9" s="5" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
@@ -2558,7 +2210,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="C10" s="4">
         <v>7.0000000000000007E-2</v>
@@ -2567,7 +2219,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="G10" s="5" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
@@ -2580,7 +2232,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C11" s="4">
         <v>0.05</v>
@@ -2589,7 +2241,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="G11" s="5" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
@@ -2602,7 +2254,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C12" s="4">
         <v>0.05</v>
@@ -2611,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="G12" s="5" t="b">
         <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
@@ -2626,7 +2278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E27DB38-9B86-476F-ADB3-257C50139E20}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2635,7 +2287,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1932462C-482C-40F7-8C16-E10683B0C6A3}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/Database 1.xlsx
+++ b/Database 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5223914A-20AF-453B-85CD-D56106D83657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1093D36F-2E03-4845-80A6-CFA5EF3B2E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample Data 2" sheetId="7" r:id="rId1"/>
@@ -37,14 +37,14 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="114">
   <si>
     <t>Test</t>
   </si>
@@ -324,12 +324,6 @@
   </si>
   <si>
     <t>Image Path</t>
-  </si>
-  <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Valid</t>
   </si>
   <si>
     <t>Field</t>
@@ -463,10 +457,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
@@ -493,7 +484,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{962C7140-9458-4E7F-884A-6E9A4E8487F2}" name="Table1" displayName="Table1" ref="A1:G11" totalsRowShown="0">
   <autoFilter ref="A1:G11" xr:uid="{962C7140-9458-4E7F-884A-6E9A4E8487F2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{60AA6AD5-C93C-4B92-85FF-D77DD40E87A5}" name="Index" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{60AA6AD5-C93C-4B92-85FF-D77DD40E87A5}" name="Index" dataDxfId="2">
       <calculatedColumnFormula>IF(ISNUMBER(A1),A1+1,0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{54099B7A-9B8C-482B-8083-4CA8C5275D84}" name="First Name"/>
@@ -508,20 +499,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:G12" totalsRowShown="0">
-  <autoFilter ref="A1:G12" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
-  <tableColumns count="7">
-    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:E12" totalsRowShown="0">
+  <autoFilter ref="A1:E12" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
+  <tableColumns count="5">
+    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID" dataDxfId="1">
       <calculatedColumnFormula>IF(ISNUMBER(A1),A1+1,1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="1" xr3:uid="{E195EB5F-6D4B-42C3-8801-919637F30006}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{191A4393-993C-4AB5-9310-5337B03C07D3}" name="Quantity On Hand"/>
     <tableColumn id="4" xr3:uid="{01AF8722-0E57-4D45-8F72-AD068B958406}" name="Image Path"/>
-    <tableColumn id="6" xr3:uid="{85B6F931-9CA9-4FF4-9FB1-406FC9E56BA6}" name="Column1"/>
-    <tableColumn id="7" xr3:uid="{AEC76C43-8C35-4A51-B34A-C477D5C7F079}" name="Valid" dataDxfId="0">
-      <calculatedColumnFormula>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</calculatedColumnFormula>
-    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1917,7 +1904,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7BC218-E894-43DE-BEC3-7A8A07868B41}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -1930,7 +1917,7 @@
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>88</v>
       </c>
@@ -1946,10 +1933,10 @@
       <c r="E1" t="s">
         <v>92</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>93</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>94</v>
       </c>
       <c r="J1" t="s">
@@ -1958,14 +1945,8 @@
       <c r="K1" t="s">
         <v>96</v>
       </c>
-      <c r="L1" t="s">
-        <v>97</v>
-      </c>
-      <c r="M1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <f t="shared" ref="A2:A5" si="0">IF(ISNUMBER(A1),A1+1,1)</f>
         <v>1</v>
@@ -1980,26 +1961,22 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K2" t="s">
-        <v>100</v>
-      </c>
-      <c r="L2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2014,26 +1991,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K3" t="s">
         <v>102</v>
       </c>
-      <c r="G3" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>89</v>
-      </c>
-      <c r="K3" t="s">
-        <v>64</v>
-      </c>
-      <c r="L3" t="s">
-        <v>103</v>
-      </c>
-      <c r="M3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2048,26 +2021,22 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G4" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="H4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" t="s">
+        <v>103</v>
       </c>
       <c r="J4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="K4" t="s">
         <v>105</v>
       </c>
-      <c r="L4" t="s">
-        <v>106</v>
-      </c>
-      <c r="M4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2082,26 +2051,22 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J5" t="s">
         <v>108</v>
       </c>
-      <c r="G5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>109</v>
       </c>
-      <c r="K5" t="s">
-        <v>100</v>
-      </c>
-      <c r="L5" t="s">
-        <v>110</v>
-      </c>
-      <c r="M5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="5">
         <f>IF(ISNUMBER(A5),A5+1,1)</f>
         <v>5</v>
@@ -2116,26 +2081,22 @@
         <v>33</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="H6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I6" t="s">
+        <v>64</v>
       </c>
       <c r="J6" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="K6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L6" t="s">
-        <v>112</v>
-      </c>
-      <c r="M6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="5">
         <f>IF(ISNUMBER(A6),A6+1,1)</f>
         <v>6</v>
@@ -2150,17 +2111,13 @@
         <v>97</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>1</v>
-      </c>
-      <c r="L7">
+        <v>100</v>
+      </c>
+      <c r="J7">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:11">
       <c r="A8" s="5">
         <f>IF(ISNUMBER(A7),A7+1,1)</f>
         <v>7</v>
@@ -2175,14 +2132,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G8" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="5">
         <f>IF(ISNUMBER(A8),A8+1,1)</f>
         <v>8</v>
@@ -2197,14 +2150,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G9" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="5">
         <f>IF(ISNUMBER(A9),A9+1,1)</f>
         <v>9</v>
@@ -2219,14 +2168,10 @@
         <v>2</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G10" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="5">
         <f>IF(ISNUMBER(A10),A10+1,1)</f>
         <v>10</v>
@@ -2241,14 +2186,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="5">
         <f>IF(ISNUMBER(A11),A11+1,1)</f>
         <v>11</v>
@@ -2263,11 +2204,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" s="5" t="b">
-        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Database 1.xlsx
+++ b/Database 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1093D36F-2E03-4845-80A6-CFA5EF3B2E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DBAB0F9-1238-46FD-9B12-AE947706DECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample Data 2" sheetId="7" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="122">
   <si>
     <t>Test</t>
   </si>
@@ -344,6 +344,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>tinyint</t>
+  </si>
+  <si>
     <t>uuid for said entry</t>
   </si>
   <si>
@@ -371,9 +374,6 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>tinyint</t>
-  </si>
-  <si>
     <t>quantity of snack</t>
   </si>
   <si>
@@ -387,6 +387,30 @@
   </si>
   <si>
     <t>juicyfruit.jpg</t>
+  </si>
+  <si>
+    <t>SalesID</t>
+  </si>
+  <si>
+    <t>uuid for snack</t>
+  </si>
+  <si>
+    <t>Snack Name</t>
+  </si>
+  <si>
+    <t>name of snack</t>
+  </si>
+  <si>
+    <t>DateTimeSold</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>date and time that the item was sold</t>
+  </si>
+  <si>
+    <t>SlotNumber</t>
   </si>
 </sst>
 </file>
@@ -1970,10 +1994,10 @@
         <v>98</v>
       </c>
       <c r="J2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1991,7 +2015,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H3" t="s">
         <v>89</v>
@@ -2000,10 +2024,10 @@
         <v>64</v>
       </c>
       <c r="J3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2027,13 +2051,13 @@
         <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2051,16 +2075,16 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I5" t="s">
         <v>98</v>
       </c>
       <c r="J5" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="K5" t="s">
         <v>109</v>
@@ -2081,7 +2105,7 @@
         <v>33</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H6" t="s">
         <v>92</v>
@@ -2111,7 +2135,7 @@
         <v>97</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J7">
         <v>15</v>
@@ -2204,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2226,9 +2250,94 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1932462C-482C-40F7-8C16-E10683B0C6A3}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Database 1.xlsx
+++ b/Database 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1093D36F-2E03-4845-80A6-CFA5EF3B2E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD6F448C-9BE2-4401-961E-4F5F6EB22374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample Data 2" sheetId="7" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="122">
   <si>
     <t>Test</t>
   </si>
@@ -344,6 +344,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>tinyint</t>
+  </si>
+  <si>
     <t>uuid for said entry</t>
   </si>
   <si>
@@ -371,9 +374,6 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>tinyint</t>
-  </si>
-  <si>
     <t>quantity of snack</t>
   </si>
   <si>
@@ -387,6 +387,30 @@
   </si>
   <si>
     <t>juicyfruit.jpg</t>
+  </si>
+  <si>
+    <t>SalesID</t>
+  </si>
+  <si>
+    <t>uuid for snack</t>
+  </si>
+  <si>
+    <t>Snack Name</t>
+  </si>
+  <si>
+    <t>name of snack</t>
+  </si>
+  <si>
+    <t>DateTimeSold</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>date and time that the item was sold</t>
+  </si>
+  <si>
+    <t>SlotNumber</t>
   </si>
 </sst>
 </file>
@@ -1970,10 +1994,10 @@
         <v>98</v>
       </c>
       <c r="J2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1991,7 +2015,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H3" t="s">
         <v>89</v>
@@ -2000,10 +2024,10 @@
         <v>64</v>
       </c>
       <c r="J3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2027,13 +2051,13 @@
         <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2051,16 +2075,16 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I5" t="s">
         <v>98</v>
       </c>
       <c r="J5" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="K5" t="s">
         <v>109</v>
@@ -2081,7 +2105,7 @@
         <v>33</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H6" t="s">
         <v>92</v>
@@ -2111,7 +2135,7 @@
         <v>97</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J7">
         <v>15</v>
@@ -2204,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2226,9 +2250,97 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1932462C-482C-40F7-8C16-E10683B0C6A3}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Database 1.xlsx
+++ b/Database 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD6F448C-9BE2-4401-961E-4F5F6EB22374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C772CFFB-169E-4FCA-B6B9-F5F010847174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample Data 2" sheetId="7" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="131">
   <si>
     <t>Test</t>
   </si>
@@ -411,14 +411,42 @@
   </si>
   <si>
     <t>SlotNumber</t>
+  </si>
+  <si>
+    <t>slot number of the location in said vending macine</t>
+  </si>
+  <si>
+    <t>SnackName</t>
+  </si>
+  <si>
+    <t>Skittles</t>
+  </si>
+  <si>
+    <t>Lays</t>
+  </si>
+  <si>
+    <t>Doritos</t>
+  </si>
+  <si>
+    <t>Diet Coke</t>
+  </si>
+  <si>
+    <t>Coke</t>
+  </si>
+  <si>
+    <t>Hubba Bubba</t>
+  </si>
+  <si>
+    <t>KitKat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -464,24 +492,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
@@ -508,7 +543,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{962C7140-9458-4E7F-884A-6E9A4E8487F2}" name="Table1" displayName="Table1" ref="A1:G11" totalsRowShown="0">
   <autoFilter ref="A1:G11" xr:uid="{962C7140-9458-4E7F-884A-6E9A4E8487F2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{60AA6AD5-C93C-4B92-85FF-D77DD40E87A5}" name="Index" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{60AA6AD5-C93C-4B92-85FF-D77DD40E87A5}" name="Index" dataDxfId="4">
       <calculatedColumnFormula>IF(ISNUMBER(A1),A1+1,0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{54099B7A-9B8C-482B-8083-4CA8C5275D84}" name="First Name"/>
@@ -526,13 +561,27 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:E12" totalsRowShown="0">
   <autoFilter ref="A1:E12" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID" dataDxfId="3">
       <calculatedColumnFormula>IF(ISNUMBER(A1),A1+1,1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="1" xr3:uid="{E195EB5F-6D4B-42C3-8801-919637F30006}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{191A4393-993C-4AB5-9310-5337B03C07D3}" name="Quantity On Hand"/>
     <tableColumn id="4" xr3:uid="{01AF8722-0E57-4D45-8F72-AD068B958406}" name="Image Path"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A77DDC88-189A-4868-B9D8-B494AF55E2FA}" name="Table3" displayName="Table3" ref="A9:E19" totalsRowShown="0">
+  <autoFilter ref="A9:E19" xr:uid="{A77DDC88-189A-4868-B9D8-B494AF55E2FA}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{85C1B6AD-32F3-4EC4-B6BD-61DE1D497D96}" name="SalesID"/>
+    <tableColumn id="2" xr3:uid="{A536900B-C5FD-4C5A-9CF9-AEACD6B62486}" name="SnackName"/>
+    <tableColumn id="3" xr3:uid="{91917D6D-85E4-48DA-B838-0BB1E44B2855}" name="Price" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{9771A8F6-B5B0-4549-8E9E-3A073CA1EB5E}" name="DateTimeSold" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{BF8DC865-B8E4-4466-AF13-95778696A5BE}" name="SlotNumber"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1514,7 +1563,7 @@
       <c r="G1" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J1" t="s">
@@ -1550,7 +1599,7 @@
       <c r="G2" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="3"/>
+      <c r="I2" s="5"/>
       <c r="J2" t="s">
         <v>45</v>
       </c>
@@ -1584,7 +1633,7 @@
       <c r="G3" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="5"/>
       <c r="J3" t="s">
         <v>33</v>
       </c>
@@ -1618,7 +1667,7 @@
       <c r="G4" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="3"/>
+      <c r="I4" s="5"/>
       <c r="J4" t="s">
         <v>34</v>
       </c>
@@ -1649,7 +1698,7 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="5"/>
       <c r="J5" t="s">
         <v>35</v>
       </c>
@@ -1686,7 +1735,7 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="I6" s="3"/>
+      <c r="I6" s="5"/>
       <c r="J6" t="s">
         <v>36</v>
       </c>
@@ -1932,7 +1981,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -1948,7 +1997,7 @@
       <c r="B1" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>90</v>
       </c>
       <c r="D1" t="s">
@@ -1978,7 +2027,7 @@
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>0.05</v>
       </c>
       <c r="D2">
@@ -2008,13 +2057,13 @@
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>101</v>
       </c>
       <c r="H3" t="s">
@@ -2038,7 +2087,7 @@
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>0.7</v>
       </c>
       <c r="D4">
@@ -2068,13 +2117,13 @@
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>0.05</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>107</v>
       </c>
       <c r="H5" t="s">
@@ -2091,20 +2140,20 @@
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="5">
+      <c r="A6">
         <f>IF(ISNUMBER(A5),A5+1,1)</f>
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D6">
         <v>33</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>101</v>
       </c>
       <c r="H6" t="s">
@@ -2121,20 +2170,20 @@
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="5">
+      <c r="A7">
         <f>IF(ISNUMBER(A6),A6+1,1)</f>
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D7">
         <v>97</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>101</v>
       </c>
       <c r="J7">
@@ -2142,92 +2191,92 @@
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="5">
+      <c r="A8">
         <f>IF(ISNUMBER(A7),A7+1,1)</f>
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>0.08</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="5">
+      <c r="A9">
         <f>IF(ISNUMBER(A8),A8+1,1)</f>
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="5">
+      <c r="A10">
         <f>IF(ISNUMBER(A9),A9+1,1)</f>
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="5">
+      <c r="A11">
         <f>IF(ISNUMBER(A10),A10+1,1)</f>
         <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>0.05</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="4" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="5">
+      <c r="A12">
         <f>IF(ISNUMBER(A11),A11+1,1)</f>
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>0.05</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="4" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2250,16 +2299,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1932462C-482C-40F7-8C16-E10683B0C6A3}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>93</v>
       </c>
@@ -2273,7 +2323,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -2287,7 +2337,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>116</v>
       </c>
@@ -2301,7 +2351,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>90</v>
       </c>
@@ -2315,7 +2365,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -2329,7 +2379,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>121</v>
       </c>
@@ -2337,10 +2387,203 @@
         <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="D6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6">
+        <v>46146</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="D11" s="6">
+        <v>46146</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="D12" s="6">
+        <v>46148</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="D13" s="6">
+        <v>46148</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="7">
+        <v>2.25</v>
+      </c>
+      <c r="D14" s="6">
+        <v>46149</v>
+      </c>
+      <c r="E14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="7">
+        <v>2.25</v>
+      </c>
+      <c r="D15" s="6">
+        <v>46149</v>
+      </c>
+      <c r="E15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="7">
+        <v>3</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46151</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D17" s="6">
+        <v>46151</v>
+      </c>
+      <c r="E17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="D18" s="6">
+        <v>46153</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1.25</v>
+      </c>
+      <c r="D19" s="6">
+        <v>46153</v>
+      </c>
+      <c r="E19">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Database 1.xlsx
+++ b/Database 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C772CFFB-169E-4FCA-B6B9-F5F010847174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EAEA1FC-BDFB-40C6-B399-2204933C6529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample Data 2" sheetId="7" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="138">
   <si>
     <t>Test</t>
   </si>
@@ -387,6 +387,27 @@
   </si>
   <si>
     <t>juicyfruit.jpg</t>
+  </si>
+  <si>
+    <t>Fields</t>
+  </si>
+  <si>
+    <t>C# datatypes</t>
+  </si>
+  <si>
+    <t>SQL datatypes</t>
+  </si>
+  <si>
+    <t>Slotnumber</t>
+  </si>
+  <si>
+    <t>ImagePath</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>QFS</t>
   </si>
   <si>
     <t>SalesID</t>
@@ -500,11 +521,11 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1563,7 +1584,7 @@
       <c r="G1" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J1" t="s">
@@ -1599,7 +1620,7 @@
       <c r="G2" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="5"/>
+      <c r="I2" s="7"/>
       <c r="J2" t="s">
         <v>45</v>
       </c>
@@ -1633,7 +1654,7 @@
       <c r="G3" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="I3" s="7"/>
       <c r="J3" t="s">
         <v>33</v>
       </c>
@@ -1667,7 +1688,7 @@
       <c r="G4" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="7"/>
       <c r="J4" t="s">
         <v>34</v>
       </c>
@@ -1698,7 +1719,7 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="7"/>
       <c r="J5" t="s">
         <v>35</v>
       </c>
@@ -1735,7 +1756,7 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="I6" s="5"/>
+      <c r="I6" s="7"/>
       <c r="J6" t="s">
         <v>36</v>
       </c>
@@ -2290,9 +2311,68 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E27DB38-9B86-476F-ADB3-257C50139E20}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2325,7 +2405,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B2" t="s">
         <v>98</v>
@@ -2334,12 +2414,12 @@
         <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -2348,7 +2428,7 @@
         <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2367,21 +2447,21 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
         <v>98</v>
@@ -2390,24 +2470,24 @@
         <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2415,12 +2495,12 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="7">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6">
+        <v>131</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
         <v>46146</v>
       </c>
       <c r="E10">
@@ -2432,12 +2512,12 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C11" s="7">
+        <v>132</v>
+      </c>
+      <c r="C11" s="6">
         <v>1.75</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>46146</v>
       </c>
       <c r="E11">
@@ -2449,12 +2529,12 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="7">
+        <v>132</v>
+      </c>
+      <c r="C12" s="6">
         <v>1.75</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>46148</v>
       </c>
       <c r="E12">
@@ -2466,12 +2546,12 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="7">
+        <v>133</v>
+      </c>
+      <c r="C13" s="6">
         <v>1.75</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>46148</v>
       </c>
       <c r="E13">
@@ -2483,12 +2563,12 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="7">
+        <v>134</v>
+      </c>
+      <c r="C14" s="6">
         <v>2.25</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>46149</v>
       </c>
       <c r="E14">
@@ -2500,12 +2580,12 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="7">
+        <v>135</v>
+      </c>
+      <c r="C15" s="6">
         <v>2.25</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>46149</v>
       </c>
       <c r="E15">
@@ -2517,12 +2597,12 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" s="7">
+        <v>136</v>
+      </c>
+      <c r="C16" s="6">
         <v>3</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>46151</v>
       </c>
       <c r="E16">
@@ -2534,12 +2614,12 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>130</v>
-      </c>
-      <c r="C17" s="7">
+        <v>137</v>
+      </c>
+      <c r="C17" s="6">
         <v>1.5</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>46151</v>
       </c>
       <c r="E17">
@@ -2551,12 +2631,12 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="7">
+        <v>134</v>
+      </c>
+      <c r="C18" s="6">
         <v>2.5</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>46153</v>
       </c>
       <c r="E18">
@@ -2568,12 +2648,12 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="7">
+        <v>137</v>
+      </c>
+      <c r="C19" s="6">
         <v>1.25</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>46153</v>
       </c>
       <c r="E19">

--- a/Database 1.xlsx
+++ b/Database 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EAEA1FC-BDFB-40C6-B399-2204933C6529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{904D3ABA-2738-4F94-9D45-B09D01F26904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="144">
   <si>
     <t>Test</t>
   </si>
@@ -401,13 +401,31 @@
     <t>Slotnumber</t>
   </si>
   <si>
+    <t>number of the location</t>
+  </si>
+  <si>
     <t>ImagePath</t>
   </si>
   <si>
     <t>text</t>
   </si>
   <si>
+    <t>location of the image</t>
+  </si>
+  <si>
+    <t>item price</t>
+  </si>
+  <si>
     <t>QFS</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>Slot Number</t>
+  </si>
+  <si>
+    <t>skittles.png</t>
   </si>
   <si>
     <t>SalesID</t>
@@ -531,9 +549,12 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
@@ -564,7 +585,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{962C7140-9458-4E7F-884A-6E9A4E8487F2}" name="Table1" displayName="Table1" ref="A1:G11" totalsRowShown="0">
   <autoFilter ref="A1:G11" xr:uid="{962C7140-9458-4E7F-884A-6E9A4E8487F2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{60AA6AD5-C93C-4B92-85FF-D77DD40E87A5}" name="Index" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{60AA6AD5-C93C-4B92-85FF-D77DD40E87A5}" name="Index" dataDxfId="5">
       <calculatedColumnFormula>IF(ISNUMBER(A1),A1+1,0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{54099B7A-9B8C-482B-8083-4CA8C5275D84}" name="First Name"/>
@@ -582,11 +603,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:E12" totalsRowShown="0">
   <autoFilter ref="A1:E12" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID" dataDxfId="3">
+    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID" dataDxfId="4">
       <calculatedColumnFormula>IF(ISNUMBER(A1),A1+1,1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="1" xr3:uid="{E195EB5F-6D4B-42C3-8801-919637F30006}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{191A4393-993C-4AB5-9310-5337B03C07D3}" name="Quantity On Hand"/>
     <tableColumn id="4" xr3:uid="{01AF8722-0E57-4D45-8F72-AD068B958406}" name="Image Path"/>
   </tableColumns>
@@ -595,6 +616,21 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{51DD5828-4B8A-48E2-B96D-D0BB889DE398}" name="Table4" displayName="Table4" ref="A7:D19" totalsRowShown="0">
+  <autoFilter ref="A7:D19" xr:uid="{51DD5828-4B8A-48E2-B96D-D0BB889DE398}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{AD90534C-4EBA-4ADA-B784-BCEC407E48B6}" name="Slot Number">
+      <calculatedColumnFormula>IF(NOT(ISNUMBER(A7)),1,A7+1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{2681EEC5-B89F-4A09-8268-D1BBCF71C831}" name="Image Path"/>
+    <tableColumn id="3" xr3:uid="{A921DEF8-D486-4CA1-A7A9-3E633BA3E744}" name="Price" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{5C82804D-8259-4B1B-8840-1E97A4AA1504}" name="QFS"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A77DDC88-189A-4868-B9D8-B494AF55E2FA}" name="Table3" displayName="Table3" ref="A9:E19" totalsRowShown="0">
   <autoFilter ref="A9:E19" xr:uid="{A77DDC88-189A-4868-B9D8-B494AF55E2FA}"/>
   <tableColumns count="5">
@@ -2311,8 +2347,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E27DB38-9B86-476F-ADB3-257C50139E20}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -2338,16 +2378,22 @@
       <c r="C2" t="s">
         <v>99</v>
       </c>
+      <c r="D2" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="D3" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2360,10 +2406,13 @@
       <c r="C4" t="s">
         <v>105</v>
       </c>
+      <c r="D4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B5" t="s">
         <v>98</v>
@@ -2371,9 +2420,209 @@
       <c r="C5" t="s">
         <v>99</v>
       </c>
+      <c r="D5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <f>IF(NOT(ISNUMBER(A7)),1,A7+1)</f>
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <f t="shared" ref="A9:A18" si="0">IF(NOT(ISNUMBER(A8)),1,A8+1)</f>
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D13">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <f>IF(NOT(ISNUMBER(A18)),1,A18+1)</f>
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -2405,7 +2654,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
         <v>98</v>
@@ -2414,12 +2663,12 @@
         <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -2428,7 +2677,7 @@
         <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2447,21 +2696,21 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
         <v>98</v>
@@ -2470,24 +2719,24 @@
         <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2495,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C10" s="6">
         <v>1</v>
@@ -2512,7 +2761,7 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C11" s="6">
         <v>1.75</v>
@@ -2529,7 +2778,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C12" s="6">
         <v>1.75</v>
@@ -2546,7 +2795,7 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C13" s="6">
         <v>1.75</v>
@@ -2563,7 +2812,7 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C14" s="6">
         <v>2.25</v>
@@ -2580,7 +2829,7 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C15" s="6">
         <v>2.25</v>
@@ -2597,7 +2846,7 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C16" s="6">
         <v>3</v>
@@ -2614,7 +2863,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C17" s="6">
         <v>1.5</v>
@@ -2631,7 +2880,7 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C18" s="6">
         <v>2.5</v>
@@ -2648,7 +2897,7 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C19" s="6">
         <v>1.25</v>
